--- a/jpcore-r4/feature/ImagingStudyTest/StructureDefinition-jp-observation-electrocardiogram.xlsx
+++ b/jpcore-r4/feature/ImagingStudyTest/StructureDefinition-jp-observation-electrocardiogram.xlsx
@@ -282,7 +282,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidまたはmeta.lastupdatedを持たないものとします / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}obs-6:databsentrasonは、観察.value [x]が存在しない場合にのみ存在するものとします / dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:visserveration.codeがvisserveration.component.codeと同じ場合、コードに関連付けられている値要素が存在しないでください / If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}obs-6:databsentrasonは、観察.value [x]が存在しない場合にのみ存在するものとします / dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:visserveration.codeがvisserveration.component.codeと同じ場合、コードに関連付けられている値要素が存在しないでください / If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -329,16 +329,16 @@
 </t>
   </si>
   <si>
-    <t>リソースに関するメタデータ / Metadata about the resource</t>
-  </si>
-  <si>
-    <t>リソースに関するメタデータ。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>リソースに関するMetadata / Metadata about the resource</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
   </si>
   <si>
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -464,7 +464,7 @@
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
@@ -1811,7 +1811,7 @@
     <t>どの値が「正常」と見なされるかを知ることは、特定の結果の意義を評価するのに役立つ。さまざまなコンテキストに対応するため複数の参照範囲を提供できる必要がある。</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 obs-3:少なくとも低いまたは高またはテキストが必要です / Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}</t>
   </si>
   <si>
